--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.140080660849014</v>
+        <v>0.8189231721319288</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.1400806608490079</v>
+        <v>-0.1810768278680776</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.025150891909552</v>
+        <v>-0.03714284522009781</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.04270157838792965</v>
+        <v>-0.02065863379291299</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2472073059547178</v>
+        <v>0.2012526188194003</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.164131164940189</v>
+        <v>-0.1611970916337194</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.232151705457029</v>
+        <v>-0.2227408414484647</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.3691317692822371</v>
+        <v>0.4621065286972506</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06813526768085273</v>
+        <v>-0.08037723536347606</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.204893327444005</v>
+        <v>0.1793111309388064</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2641684152679836</v>
+        <v>-0.1053443488793229</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3229400938622092</v>
+        <v>0.3650903514443965</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年06月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>18.74849055325728</v>
+        <v>13.43168476517357</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07496239909761963</v>
+        <v>0.05370412679677973</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1803739432546652</v>
+        <v>0.1330524962088818</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>3.21203007518797</v>
+        <v>3.623308270676692</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
